--- a/plantillas/eventos.xlsx
+++ b/plantillas/eventos.xlsx
@@ -981,7 +981,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>ev-045</t>
+          <t>ev-073</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -991,43 +991,43 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>19.744</v>
+        <v>19.028</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-99.18000000000001</v>
+        <v>-99.271</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Teoloyucan, Estado de México</t>
+          <t>Huitzilac, Morelos</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Calletano de Jesús Guerrero, Global México</t>
+          <t>Asesinato de Silvia Hernández Meza, defensora del bosque de Huitzilac</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Asesinado con arma de fuego en el estacionamiento de una parroquia. Cuatro días antes había recibido amenazas de muerte en su domicilio y el Mecanismo federal había activado su reubicación urgente. La fiscalía estatal lo vinculó después con grupos delictivos sin contactar a su familia. Ubicación aproximada (cabecera municipal).</t>
+          <t>Candidata a presidir los bienes comunales, reconocida por Conafor por su trabajo de reforestación y denuncia de la tala en el Parque Nacional Lagunas de Zempoala; asesinada con cuatro integrantes de su planilla durante la campaña. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -1044,125 +1044,133 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>ev-005</t>
+          <t>ev-045</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>desaparicion</t>
+          <t>periodistas</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>búsqueda en campo</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>26.4222</v>
+        <v>19.744</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-108.6203</v>
+        <v>-99.18000000000001</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>El Fuerte, Sinaloa</t>
+          <t>Teoloyucan, Estado de México</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Ejemplo: jornada de búsqueda de colectivo</t>
+          <t>Asesinato de Calletano de Jesús Guerrero, Global México</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Registro de ejemplo. Campos sugeridos: colectivo, hallazgos, autoridades presentes.</t>
+          <t>Asesinado con arma de fuego en el estacionamiento de una parroquia. Cuatro días antes había recibido amenazas de muerte en su domicilio y el Mecanismo federal había activado su reubicación urgente. La fiscalía estatal lo vinculó después con grupos delictivos sin contactar a su familia. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>ceb-sin</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+          <t>article19</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>campo</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ev-001</t>
+          <t>ev-074</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>migracion</t>
+          <t>periodistas</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>albergue</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>23.2329</v>
+        <v>16.963</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-106.4062</v>
+        <v>-95.093</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Mazatlán, Sinaloa</t>
+          <t>San Juan Guichicovi, Oaxaca</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Ejemplo: albergue para personas en tránsito</t>
+          <t>Asesinato de Arnoldo Nicolás Romero, comisario ejidal e integrante de UCIZONI</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Registro de ejemplo. Reemplazar con datos de campo (capacidad, personas atendidas por mes).</t>
+          <t>Opositor a la imposición del Corredor Interoceánico; reportado desaparecido el 17 de enero y hallado sin vida el 21 con heridas de bala y quemaduras. Sin datos de investigación en curso. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>ceb-sin</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
+          <t>cemda</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
+        </is>
+      </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>sin verificar</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>ev-046</t>
+          <t>ev-075</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1172,43 +1180,43 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>20.941</v>
+        <v>19.947</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-101.428</v>
+        <v>-97.553</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Silao, Guanajuato</t>
+          <t>Acuaco, Zaragoza, Puebla</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Kristian Uriel Martínez Zavala, El Silaoense MX</t>
+          <t>Asesinato de José Luis Lucas Quirino, profesor y líder ejidal</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (cabecera municipal).</t>
+          <t>Defensor del agua y los bosques de la Sierra Nororiental frente a granjas porcícolas y minería; atacado con armas de fuego frente a la primaria que dirigía. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -1225,70 +1233,66 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>ev-047</t>
+          <t>ev-005</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>periodistas</t>
+          <t>desaparicion</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>cifra oficial</t>
+          <t>búsqueda en campo</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>24.809</v>
+        <v>26.4222</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-107.394</v>
+        <v>-108.6203</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Culiacán, Sinaloa</t>
+          <t>El Fuerte, Sinaloa</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Instituto de Protección de Sinaloa atiende a 77 periodistas y defensores en medio año de crisis</t>
+          <t>Ejemplo: jornada de búsqueda de colectivo</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>En seis meses de la pugna entre facciones del Cártel de Sinaloa, el Instituto otorgó 333 medidas cautelares a periodistas, activistas y 16 familiares. Agresiones más comunes: amenazas, disparos contra medios, daños a vehículos y viviendas, privación de la libertad y censura. Ubicación aproximada (cabecera municipal).</t>
+          <t>Registro de ejemplo. Campos sugeridos: colectivo, hallazgos, autoridades presentes.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>instituto-sinaloa</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>https://www.noroeste.com.mx/culiacan/atiende-instituto-de-proteccion-a-77-periodistas-y-activistas-de-sinaloa-en-medio-de-crisis-de-violencia-BI11082146</t>
-        </is>
-      </c>
+          <t>ceb-sin</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr"/>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>campo</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>ev-048</t>
+          <t>ev-076</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1298,43 +1302,43 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>agresión física por autoridad</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>17.989</v>
+        <v>15.832</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-92.93000000000001</v>
+        <v>-95.953</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Villahermosa, Tabasco</t>
+          <t>Barra de la Cruz, Santiago Astata, Oaxaca</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Fotoperiodista de El Universal lesionado por agente de seguridad estatal durante cobertura</t>
+          <t>Asesinato de Cristino Castro Perea, defensor del santuario de tortugas de Barra de la Cruz</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Derribado y golpeado por una persona en función policial de la Secretaría de Seguridad de Tabasco mientras cubría un homicidio. ARTICLE 19 registró 53 agresiones físicas en 2025, con participación recurrente de agentes del Estado. Ubicación aproximada (cabecera municipal).</t>
+          <t>Fundador del colectivo Defensores Ambientalistas de Barra de la Cruz y beneficiario del Mecanismo federal; dos personas en motocicleta le dispararon en el quiosco de su comunidad. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -1351,121 +1355,117 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>ev-049</t>
+          <t>ev-001</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>periodistas</t>
+          <t>migracion</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>albergue</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>21.298</v>
+        <v>23.2329</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-100.517</v>
+        <v>-106.4062</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>San Luis de la Paz, Guanajuato</t>
+          <t>Mazatlán, Sinaloa</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Raúl Irán Villarreal Belmont, Observatorio Ciudadano San Luis de la Paz</t>
+          <t>Ejemplo: albergue para personas en tránsito</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (cabecera municipal).</t>
+          <t>Registro de ejemplo. Reemplazar con datos de campo (capacidad, personas atendidas por mes).</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
-        </is>
-      </c>
+          <t>ceb-sin</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>sin verificar</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>ev-014</t>
+          <t>ev-046</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
+          <t>periodistas</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>19.088</v>
+        <v>20.941</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-102.353</v>
+        <v>-101.428</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Apatzingán, Michoacán</t>
+          <t>Silao, Guanajuato</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Cerca de 500 familias desplazadas de la zona rural de Apatzingán desde inicios de 2025</t>
+          <t>Asesinato de Kristian Uriel Martínez Zavala, El Silaoense MX</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Una diputada local informó que desde inicios de 2025 unas 500 familias habían salido de localidades como Las Huertas, El Alcalde, El Guayabo, Holanda, El Morado, Bateas, Loma de Los Hoyos y Presa del Rosario por minas terrestres y enfrentamientos; más de 300 habían regresado y unas 150 seguían fuera. Ubicación aproximada (cabecera municipal).</t>
+          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>jornada</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://www.jornada.com.mx/noticia/2025/03/31/estados/cerca-de-500-familias-en-michoacan-se-han-desplazado-de-manera-forzada</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1477,53 +1477,53 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>ev-015</t>
+          <t>ev-047</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
+          <t>periodistas</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>padrón oficial</t>
+          <t>cifra oficial</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>23.284</v>
+        <v>24.809</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-106.069</v>
+        <v>-107.394</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Concordia, Sinaloa</t>
+          <t>Culiacán, Sinaloa</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>Padrón Sebides: 261 familias desplazadas en Concordia (septiembre 2024 a marzo 2025)</t>
+          <t>Instituto de Protección de Sinaloa atiende a 77 periodistas y defensores en medio año de crisis</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Concordia corresponden 261 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
+          <t>En seis meses de la pugna entre facciones del Cártel de Sinaloa, el Instituto otorgó 333 medidas cautelares a periodistas, activistas y 16 familiares. Agresiones más comunes: amenazas, disparos contra medios, daños a vehículos y viviendas, privación de la libertad y censura. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>instituto-sinaloa</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://riodoce.mx/2025/04/07/mas-de-800-familias-desplazadas-por-la-violencia-en-sinaloa/</t>
+          <t>https://www.noroeste.com.mx/culiacan/atiende-instituto-de-proteccion-a-77-periodistas-y-activistas-de-sinaloa-en-medio-de-crisis-de-violencia-BI11082146</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -1540,58 +1540,58 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>ev-016</t>
+          <t>ev-048</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
+          <t>periodistas</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>padrón oficial</t>
+          <t>agresión física por autoridad</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>24.412</v>
+        <v>17.989</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-106.69</v>
+        <v>-92.93000000000001</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Cosalá, Sinaloa</t>
+          <t>Villahermosa, Tabasco</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Padrón Sebides: 238 familias desplazadas en Cosalá (septiembre 2024 a marzo 2025)</t>
+          <t>Fotoperiodista de El Universal lesionado por agente de seguridad estatal durante cobertura</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Cosalá corresponden 238 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
+          <t>Derribado y golpeado por una persona en función policial de la Secretaría de Seguridad de Tabasco mientras cubría un homicidio. ARTICLE 19 registró 53 agresiones físicas en 2025, con participación recurrente de agentes del Estado. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://riodoce.mx/2025/04/07/mas-de-800-familias-desplazadas-por-la-violencia-en-sinaloa/</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -1603,58 +1603,58 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>ev-017</t>
+          <t>ev-049</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
+          <t>periodistas</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>padrón oficial</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>24.809</v>
+        <v>21.298</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-107.394</v>
+        <v>-100.517</v>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Culiacán, Sinaloa</t>
+          <t>San Luis de la Paz, Guanajuato</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>Padrón Sebides: 127 familias desplazadas en Culiacán (septiembre 2024 a marzo 2025)</t>
+          <t>Asesinato de Raúl Irán Villarreal Belmont, Observatorio Ciudadano San Luis de la Paz</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Culiacán corresponden 127 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
+          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://riodoce.mx/2025/04/07/mas-de-800-familias-desplazadas-por-la-violencia-en-sinaloa/</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>ev-018</t>
+          <t>ev-014</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1676,48 +1676,48 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>padrón oficial</t>
+          <t>desplazamiento masivo</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>22.991</v>
+        <v>19.088</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-105.857</v>
+        <v>-102.353</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Rosario, Sinaloa</t>
+          <t>Apatzingán, Michoacán</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Padrón Sebides: 65 familias desplazadas en Rosario (septiembre 2024 a marzo 2025)</t>
+          <t>Cerca de 500 familias desplazadas de la zona rural de Apatzingán desde inicios de 2025</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Rosario corresponden 65 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
+          <t>Una diputada local informó que desde inicios de 2025 unas 500 familias habían salido de localidades como Las Huertas, El Alcalde, El Guayabo, Holanda, El Morado, Bateas, Loma de Los Hoyos y Presa del Rosario por minas terrestres y enfrentamientos; más de 300 habían regresado y unas 150 seguían fuera. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>jornada</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://riodoce.mx/2025/04/07/mas-de-800-familias-desplazadas-por-la-violencia-en-sinaloa/</t>
+          <t>https://www.jornada.com.mx/noticia/2025/03/31/estados/cerca-de-500-familias-en-michoacan-se-han-desplazado-de-manera-forzada</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>ev-019</t>
+          <t>ev-015</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1748,24 +1748,24 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>23.921</v>
+        <v>23.284</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-106.892</v>
+        <v>-106.069</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Elota, Sinaloa</t>
+          <t>Concordia, Sinaloa</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Padrón Sebides: 41 familias desplazadas en Elota (septiembre 2024 a marzo 2025)</t>
+          <t>Padrón Sebides: 261 familias desplazadas en Concordia (septiembre 2024 a marzo 2025)</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Elota corresponden 41 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
+          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Concordia corresponden 261 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1792,7 +1792,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>ev-020</t>
+          <t>ev-016</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1811,24 +1811,24 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>23.936</v>
+        <v>24.412</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>-106.425</v>
+        <v>-106.69</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>San Ignacio, Sinaloa</t>
+          <t>Cosalá, Sinaloa</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Padrón Sebides: 40 familias desplazadas en San Ignacio (septiembre 2024 a marzo 2025)</t>
+          <t>Padrón Sebides: 238 familias desplazadas en Cosalá (septiembre 2024 a marzo 2025)</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a San Ignacio corresponden 40 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
+          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Cosalá corresponden 238 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1855,7 +1855,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>ev-021</t>
+          <t>ev-017</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1874,24 +1874,24 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>24.765</v>
+        <v>24.809</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-107.702</v>
+        <v>-107.394</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Navolato, Sinaloa</t>
+          <t>Culiacán, Sinaloa</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Padrón Sebides: 38 familias desplazadas en Navolato (septiembre 2024 a marzo 2025)</t>
+          <t>Padrón Sebides: 127 familias desplazadas en Culiacán (septiembre 2024 a marzo 2025)</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Navolato corresponden 38 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
+          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Culiacán corresponden 127 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1918,58 +1918,58 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>ev-050</t>
+          <t>ev-018</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>periodistas</t>
+          <t>desplazamiento</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>desaparición de periodista</t>
+          <t>padrón oficial</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>22.055</v>
+        <v>22.991</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-98.18300000000001</v>
+        <v>-105.857</v>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Pánuco, Veracruz</t>
+          <t>Rosario, Sinaloa</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>Desaparición de Miguel Ángel Anaya Castillo, director de Pánuco On Line</t>
+          <t>Padrón Sebides: 65 familias desplazadas en Rosario (septiembre 2024 a marzo 2025)</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Desaparecido desde el 13 de abril de 2025; mes y medio antes había sido hostigado en su domicilio. ARTICLE 19 contabiliza 32 periodistas desaparecidos desde 2000, concentrados en Tamaulipas, Veracruz y Michoacán. Ubicación aproximada (cabecera municipal).</t>
+          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Rosario corresponden 65 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>sebides</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+          <t>https://riodoce.mx/2025/04/07/mas-de-800-familias-desplazadas-por-la-violencia-en-sinaloa/</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>oficial</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -1981,58 +1981,58 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>ev-051</t>
+          <t>ev-019</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>periodistas</t>
+          <t>desplazamiento</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>padrón oficial</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>16.863</v>
+        <v>23.921</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-99.88200000000001</v>
+        <v>-106.892</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Acapulco, Guerrero</t>
+          <t>Elota, Sinaloa</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de José Carlos González Herrera, El Guerrero / Opinión Ciudadana</t>
+          <t>Padrón Sebides: 41 familias desplazadas en Elota (septiembre 2024 a marzo 2025)</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (cabecera municipal).</t>
+          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Elota corresponden 41 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>sebides</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+          <t>https://riodoce.mx/2025/04/07/mas-de-800-familias-desplazadas-por-la-violencia-en-sinaloa/</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>oficial</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2044,117 +2044,121 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>ev-002</t>
+          <t>ev-020</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>migracion</t>
+          <t>desplazamiento</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>rescate</t>
+          <t>padrón oficial</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>24.8091</v>
+        <v>23.936</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-107.394</v>
+        <v>-106.425</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Culiacán, Sinaloa</t>
+          <t>San Ignacio, Sinaloa</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>Ejemplo: personas migrantes rescatadas en carretera</t>
+          <t>Padrón Sebides: 40 familias desplazadas en San Ignacio (septiembre 2024 a marzo 2025)</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Registro de ejemplo basado en nota de prensa. Reemplazar.</t>
+          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a San Ignacio corresponden 40 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>prensa-local</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
+          <t>sebides</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>https://riodoce.mx/2025/04/07/mas-de-800-familias-desplazadas-por-la-violencia-en-sinaloa/</t>
+        </is>
+      </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>oficial</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>ev-052</t>
+          <t>ev-021</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>periodistas</t>
+          <t>desplazamiento</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>amenaza</t>
+          <t>padrón oficial</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>20.674</v>
+        <v>24.765</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-103.347</v>
+        <v>-107.702</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Guadalajara, Jalisco</t>
+          <t>Navolato, Sinaloa</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Periodista encuentra nota de amenaza de muerte dentro de su camioneta</t>
+          <t>Padrón Sebides: 38 familias desplazadas en Navolato (septiembre 2024 a marzo 2025)</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>El 25 de junio de 2025 una periodista halló roto un cristal de su vehículo y una nota con la leyenda 'Te vas a morir'; ARTICLE 19 exigió acción inmediata del Estado. En 2025 la organización documentó 110 amenazas, una cada cuatro días. Ubicación aproximada (cabecera municipal).</t>
+          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Navolato corresponden 38 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>sebides</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+          <t>https://riodoce.mx/2025/04/07/mas-de-800-familias-desplazadas-por-la-violencia-en-sinaloa/</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>oficial</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2166,58 +2170,58 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>ev-022</t>
+          <t>ev-050</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
+          <t>periodistas</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>cifra oficial</t>
+          <t>desaparición de periodista</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>23.936</v>
+        <v>22.055</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>-106.425</v>
+        <v>-98.18300000000001</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>San Ignacio, Sinaloa</t>
+          <t>Pánuco, Veracruz</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>Sebides: padrón histórico de 3 mil 48 personas desplazadas; en San Ignacio el desplazamiento es permanente</t>
+          <t>Desaparición de Miguel Ángel Anaya Castillo, director de Pánuco On Line</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>La titular de Sebides distinguió un padrón histórico de 3 mil 48 personas (Choix, El Fuerte, Ahome, Sinaloa, Guasave, Salvador Alvarado, Culiacán, Mazatlán, Concordia, Rosario) y un registro preventivo de familias que van y vienen; en San Ignacio las familias de comunidades serranas ya no volverán y el municipio busca terreno para vivienda. Ubicación aproximada (cabecera municipal).</t>
+          <t>Desaparecido desde el 13 de abril de 2025; mes y medio antes había sido hostigado en su domicilio. ARTICLE 19 contabiliza 32 periodistas desaparecidos desde 2000, concentrados en Tamaulipas, Veracruz y Michoacán. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>https://lineadirectaportal.com/sinaloa/mas-de-3-mil-desplazados-en-sinaloa-en-san-ignacio-el-desplazamiento-es-permanente-sebides-2025-06-28__1422180</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -2229,7 +2233,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>ev-053</t>
+          <t>ev-078</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2239,43 +2243,43 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>27.493</v>
+        <v>20.773</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-109.938</v>
+        <v>-103.693</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Ciudad Obregón, Sonora</t>
+          <t>El Arenal, Jalisco</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Ángel Sevilla, Noticias 644</t>
+          <t>Desaparición y asesinato de Karina Ruiz Ocampo, defensora del derecho al agua</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (el informe solo indica Sonora).</t>
+          <t>Representante legal de la asociación vecinal La Cima, Nuestra Prioridad; sacada de su casa por la fuerza el 14 de abril y hallada sin vida el 3 de mayo. Se investiga como feminicidio. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -2292,7 +2296,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>ev-054</t>
+          <t>ev-077</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2302,43 +2306,43 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>16.863</v>
+        <v>16.982</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-99.88200000000001</v>
+        <v>-99.7</v>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Acapulco, Guerrero</t>
+          <t>Cacahuatepec, Acapulco, Guerrero</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Ronald Paz Pedro, NotiExpress Pedro</t>
+          <t>Ataque mortal contra Marco Antonio Suástegui, líder del CECOP</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Segundo periodista asesinado en Acapulco en 2025, según ARTICLE 19 y RSF. Ubicación aproximada (cabecera municipal).</t>
+          <t>Defensor del río Papagayo y opositor histórico a la presa La Parota; atacado al salir de la playa Icacos y fallecido ocho días después. Su familia estaba incorporada al Mecanismo tras la desaparición de su hermano en 2021. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -2355,53 +2359,53 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>ev-023</t>
+          <t>ev-051</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
+          <t>periodistas</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>25.363</v>
+        <v>16.863</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-107.551</v>
+        <v>-99.88200000000001</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>San Miguel, sierra de Badiraguato, Sinaloa</t>
+          <t>Acapulco, Guerrero</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>54 familias de San Miguel se desplazan a Hidalgo del Parral, Chihuahua</t>
+          <t>Asesinato de José Carlos González Herrera, El Guerrero / Opinión Ciudadana</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Según el informe de la Misión Civil de Observación en Chihuahua, 54 familias de la comunidad de San Miguel, a cinco horas de Badiraguato y dos de Atascaderos, salieron en septiembre de 2025 hacia Chihuahua y residen en Parral. Ubicación aproximada (cabecera de Badiraguato).</t>
+          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>mco-chihuahua</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>https://www.eldiariodechihuahua.mx/estado/2026/sep/24/llegan-desplazados-de-durango-y-sinaloa-840648.html</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -2418,55 +2422,51 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>ev-024</t>
+          <t>ev-002</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
+          <t>migracion</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>rescate</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>25</v>
+        <v>24.8091</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>-107.38</v>
+        <v>-107.394</v>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Tepuche, Culiacán, Sinaloa</t>
+          <t>Culiacán, Sinaloa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>328 familias salen de la zona serrana de Tepuche; Tachinolpa, Guayabito y Ayuné quedan sin población</t>
+          <t>Ejemplo: personas migrantes rescatadas en carretera</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>La violencia en la sierra al norte de Culiacán desplazó a 328 familias; cinco escuelas de Culiacán, Mocorito y Navolato pasaron a clases a distancia. Sebides reportó que el padrón estatal llegaba a mil 61 familias y que Ayuné podría repoblarse si se restablecen agua y caminos. Ubicación aproximada (sindicatura de Tepuche).</t>
+          <t>Registro de ejemplo basado en nota de prensa. Reemplazar.</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>sillarota</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>https://lasillarota.com/estados/2025/9/17/violencia-en-sinaloa-obliga-desplazamientos-clases-en-linea-467963.html</t>
-        </is>
-      </c>
+          <t>prensa-local</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr"/>
       <c r="L32" s="3" t="inlineStr">
         <is>
           <t>prensa</t>
@@ -2474,14 +2474,14 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>ev-055</t>
+          <t>ev-052</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2491,33 +2491,33 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>amenaza</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>24.027</v>
+        <v>20.674</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-104.653</v>
+        <v>-103.347</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Durango, Durango</t>
+          <t>Guadalajara, Jalisco</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Miguel Ángel Beltrán Martínez, periodista independiente</t>
+          <t>Periodista encuentra nota de amenaza de muerte dentro de su camioneta</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (el informe solo indica Durango).</t>
+          <t>El 25 de junio de 2025 una periodista halló roto un cristal de su vehículo y una nota con la leyenda 'Te vas a morir'; ARTICLE 19 exigió acción inmediata del Estado. En 2025 la organización documentó 110 amenazas, una cada cuatro días. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2544,7 +2544,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>ev-025</t>
+          <t>ev-022</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2554,48 +2554,48 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>cifra oficial</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>22.837</v>
+        <v>23.936</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>-105.776</v>
+        <v>-106.425</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>El Tecomatillo, Escuinapa, Sinaloa</t>
+          <t>San Ignacio, Sinaloa</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>Comunidad tepehuana de El Tecomatillo desplazada por enfrentamientos</t>
+          <t>Sebides: padrón histórico de 3 mil 48 personas desplazadas; en San Ignacio el desplazamiento es permanente</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Familias tepehuanas que habían llegado a Escuinapa huyendo de la violencia en Durango fueron desplazadas de nuevo desde diciembre de 2025, cuando los enfrentamientos destruyeron viviendas junto al arroyo Buñigas; no figuran en el padrón estatal. Fecha aproximada. Ubicación aproximada (cabecera de Escuinapa).</t>
+          <t>La titular de Sebides distinguió un padrón histórico de 3 mil 48 personas (Choix, El Fuerte, Ahome, Sinaloa, Guasave, Salvador Alvarado, Culiacán, Mazatlán, Concordia, Rosario) y un registro preventivo de familias que van y vienen; en San Ignacio las familias de comunidades serranas ya no volverán y el municipio busca terreno para vivienda. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>noroeste</t>
+          <t>sebides</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>https://www.noroeste.com.mx/mazatlan/dejaron-durango-huyendo-de-la-violencia-y-llegaron-a-escuinapa-donde-tambien-han-tenido-que-escapar-GB23220512</t>
+          <t>https://lineadirectaportal.com/sinaloa/mas-de-3-mil-desplazados-en-sinaloa-en-san-ignacio-el-desplazamiento-es-permanente-sebides-2025-06-28__1422180</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>oficial</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -2607,7 +2607,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>ev-056</t>
+          <t>ev-079</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2617,43 +2617,43 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>acoso judicial</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>19.043</v>
+        <v>19.684</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-98.19799999999999</v>
+        <v>-101.954</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Puebla, Puebla</t>
+          <t>Cherán, Michoacán</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Vinculación a proceso del director del portal e-consulta por su labor periodística</t>
+          <t>Asesinato de Francisco Macías Sánchez, integrante de la ronda comunitaria de Cherán</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>ARTICLE 19 señaló el caso como precedente grave de uso del derecho penal para intimidar. En 2025 documentó 69 periodistas y medios víctimas de acoso judicial en 21 entidades. Ubicación aproximada (cabecera municipal).</t>
+          <t>De 18 años, patrullaba el bosque comunal cuando un grupo del crimen organizado atacó a la ronda en las afueras del Rancho de Pino; otro comunero resultó herido. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -2670,7 +2670,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ev-057</t>
+          <t>ev-053</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2680,33 +2680,33 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>acoso judicial</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>18.134</v>
+        <v>27.493</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>-94.422</v>
+        <v>-109.938</v>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Coatzacoalcos, Veracruz</t>
+          <t>Ciudad Obregón, Sonora</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>Fiscalía de Veracruz imputa a periodista por terrorismo por hechos ligados a su labor</t>
+          <t>Asesinato de Ángel Sevilla, Noticias 644</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>La imputación fue desestimada, pero se mantenían vigentes otras dos. ARTICLE 19 la calificó como uno de los episodios más alarmantes del año. Ubicación aproximada (cabecera municipal).</t>
+          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (el informe solo indica Sonora).</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2733,7 +2733,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ev-058</t>
+          <t>ev-054</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2748,43 +2748,43 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>20.533</v>
+        <v>16.863</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-97.459</v>
+        <v>-99.88200000000001</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Poza Rica, Veracruz</t>
+          <t>Acapulco, Guerrero</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Carlos Castro en Poza Rica</t>
+          <t>Asesinato de Ronald Paz Pedro, NotiExpress Pedro</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Asesinado el 8 de enero dentro de un restaurante de la avenida 20 de Noviembre, primer periodista asesinado en 2026 según el recuento de N+ y CPJ. Ubicación aproximada (cabecera municipal).</t>
+          <t>Segundo periodista asesinado en Acapulco en 2025, según ARTICLE 19 y RSF. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>nmas</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>https://www.nmas.com.mx/seguridad/asesinatos/cuantos-y-quienes-son-los-periodistas-asesinados-en-mexico-este-2026/</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -2796,58 +2796,58 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ev-026</t>
+          <t>ev-080</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
+          <t>periodistas</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>24.765</v>
+        <v>17.546</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>-107.702</v>
+        <v>-98.577</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Las Puentes, Navolato, Sinaloa</t>
+          <t>Tlapa de Comonfort, Guerrero</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>Familias de Las Puentes se dispersan hacia Culiacán, Villa Juárez y El Diez</t>
+          <t>Asesinato de Sergio Hugo Ureiro Castañeda, defensor de la Plazuela de los Cántaros</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Sebides informó que en enero recorrió Las Puentes, donde algunas personas permanecieron y otras se trasladaron a Culiacán, Villa Juárez y El Diez; la dependencia seguía localizando a las familias. Ubicación aproximada (cabecera de Navolato).</t>
+          <t>Líder del movimiento que recuperó la plaza pública y área verde de Tlapa; un mes antes su casa fue incendiada. Asesinado en una gasolinera del centro. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>https://www.aztecasinaloa.com/noticias/en-sinaloa-familias-se-desplazan-por-violencia-cuales-son-los-municipios-afectados/</t>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -2859,58 +2859,58 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>ev-059</t>
+          <t>ev-023</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>periodistas</t>
+          <t>desplazamiento</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>agresión por autoridad</t>
+          <t>desplazamiento masivo</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>24.809</v>
+        <v>25.363</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-107.394</v>
+        <v>-107.551</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Culiacán, Sinaloa</t>
+          <t>San Miguel, sierra de Badiraguato, Sinaloa</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Policía estatal apunta su arma contra reportero de la fuente de seguridad</t>
+          <t>54 familias de San Miguel se desplazan a Hidalgo del Parral, Chihuahua</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Tras un enfrentamiento entre fuerzas de seguridad y un grupo armado, agentes de la Policía Estatal Preventiva agredieron a un reportero; el hecho quedó en video. El Instituto de Protección documentó 235 agresiones al gremio entre 2022 y 2025. Ubicación aproximada (cabecera municipal).</t>
+          <t>Según el informe de la Misión Civil de Observación en Chihuahua, 54 familias de la comunidad de San Miguel, a cinco horas de Badiraguato y dos de Atascaderos, salieron en septiembre de 2025 hacia Chihuahua y residen en Parral. Ubicación aproximada (cabecera de Badiraguato).</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>proceso</t>
+          <t>mco-chihuahua</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>https://www.proceso.com.mx/nacional/estados/2026/1/19/policia-estatal-de-sinaloa-apunta-su-arma-hacia-reportero-en-culiacan-video-366842.html</t>
+          <t>https://www.eldiariodechihuahua.mx/estado/2026/sep/24/llegan-desplazados-de-durango-y-sinaloa-840648.html</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -2922,7 +2922,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ev-027</t>
+          <t>ev-024</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2937,38 +2937,38 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>26.095</v>
+        <v>25</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-106.965</v>
+        <v>-107.38</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Atascaderos, Guadalupe y Calvo, Chihuahua</t>
+          <t>Tepuche, Culiacán, Sinaloa</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>Unas 600 personas desplazadas del seccional Atascaderos por enfrentamientos entre facciones</t>
+          <t>328 familias salen de la zona serrana de Tepuche; Tachinolpa, Guayabito y Ayuné quedan sin población</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Entre el 18 y el 27 de febrero cientos de personas, en su mayoría indígenas, fueron atendidas en albergues de Chihuahua capital y Parral; otras llegaron a Cuauhtémoc y Delicias. Un mes después unas 200 regresaron con acompañamiento policial y militar. Organizaciones como Alianza Sierra Madre y Contec advierten un desplazamiento silencioso que ha vaciado pueblos. Ubicación aproximada (cabecera de Guadalupe y Calvo).</t>
+          <t>La violencia en la sierra al norte de Culiacán desplazó a 328 familias; cinco escuelas de Culiacán, Mocorito y Navolato pasaron a clases a distancia. Sebides reportó que el padrón estatal llegaba a mil 61 familias y que Ayuné podría repoblarse si se restablecen agua y caminos. Ubicación aproximada (sindicatura de Tepuche).</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>elimparcial</t>
+          <t>sillarota</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>https://www.elimparcial.com/mexico/2026/04/18/indigenas-raramuri-son-desplazados-por-la-violencia-del-crimen-organizado-en-la-sierra-tarahumara-mientras-organizaciones-civiles-alertan-abandono-del-estado-y-una-crisis-humanitaria-que-ya-afecta-a-miles-de-familias-en-chihuahua/</t>
+          <t>https://lasillarota.com/estados/2025/9/17/violencia-en-sinaloa-obliga-desplazamientos-clases-en-linea-467963.html</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -2985,58 +2985,58 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ev-028</t>
+          <t>ev-055</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
+          <t>periodistas</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>cifra oficial</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>24.809</v>
+        <v>24.027</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-107.394</v>
+        <v>-104.653</v>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Culiacán, Sinaloa</t>
+          <t>Durango, Durango</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Sebides: padrón de unas 3 mil personas y mil 300 familias más desde noviembre de 2025</t>
+          <t>Asesinato de Miguel Ángel Beltrán Martínez, periodista independiente</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>El titular de Sebides informó un padrón de alrededor de 3 mil personas en desplazamiento forzado interno y mil 300 familias adicionales detectadas desde finales de 2025; Culiacán, Mazatlán y Guasave concentran la llegada. Se anunció el programa Viviendas para el Bienestar para víctimas sin casa propia. Cifra estatal ubicada en la capital.</t>
+          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (el informe solo indica Durango).</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>https://revistaespejo.com/2026/03/14/gobierno-de-sinaloa-registra-mas-de-4-mil-personas-desplazadas/</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -3048,7 +3048,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ev-060</t>
+          <t>ev-081</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -3058,33 +3058,33 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>asesinato de persona defensora</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>19.392</v>
+        <v>19.237</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>-101.278</v>
+        <v>-104.567</v>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>El Zangarro, Villa Madero, Michoacán</t>
+          <t>Cihuatlán, Jalisco</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Roberto Chávez, Comité de Defensa Ambiental de El Zangarro</t>
+          <t>Asesinato de Cándido Esaú Román Pérez, abogado y representante ejidal</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Defensor ambiental de 64 años, asesinado a balazos la noche del 12 de abril al regresar a su casa. CEMDA contabiliza al menos 195 personas defensoras ambientales asesinadas en México entre 2016 y 2026. Ubicación aproximada (cabecera municipal).</t>
+          <t>Defendía al ejido General Emiliano Zapata frente al despojo de tierras en Melaque, con amparo obtenido; asesinado afuera de su casa. La fiscalía reconoce su activismo como línea principal. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>https://grupoanimal.mx/explicaciones/defensores-ambientales-asesinados-mexico</t>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -3111,7 +3111,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ev-061</t>
+          <t>ev-082</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3121,33 +3121,33 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>desaparición y asesinato de persona defensora</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>19.401</v>
+        <v>22.345</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>-101.732</v>
+        <v>-103.605</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Zirahuén, Salvador Escalante, Michoacán</t>
+          <t>Azqueltán, Villa Guerrero, Jalisco</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Lázaro Mendoza Ramírez, defensor de la región lacustre de Zirahuén, desaparecido y hallado sin vida</t>
+          <t>Asesinato de Marcos Aguilar Rojas, representante agrario de Azqueltán</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Desaparecido el 14 de abril; su cuerpo fue localizado calcinado en su camioneta e identificado por ADN. Segundo defensor ambiental asesinado en Michoacán en menos de una semana. Ubicación aproximada (cabecera municipal).</t>
+          <t>Comunidad tepehuana-wixárika en juicio agrario por 45 mil hectáreas; atacado con su hermano al retirar ganado invasor en el predio comunal El Caracol. Los agresores están identificados y sin proceso. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>https://grupoanimal.mx/sociedad/ambientalistas-asesinados-semana-michoacan</t>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ev-029</t>
+          <t>ev-025</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3189,43 +3189,43 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>24.968</v>
+        <v>22.837</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>-106.965</v>
+        <v>-105.776</v>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Tamazula, Durango</t>
+          <t>El Tecomatillo, Escuinapa, Sinaloa</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>Al menos 368 personas desplazadas de Tamazula por enfrentamientos y amenazas de reclutamiento</t>
+          <t>Comunidad tepehuana de El Tecomatillo desplazada por enfrentamientos</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Según el informe sobre desplazamiento forzado en Chihuahua (mayo de 2026), al menos 368 personas de Tamazula, en el Triángulo Dorado, salieron por enfrentamientos, bloqueos de rutas, desabasto y amenazas de reclutamiento de jóvenes; la cabecera solo es accesible por aire desde El Durazno. Fecha del informe. Ubicación aproximada (cabecera municipal).</t>
+          <t>Familias tepehuanas que habían llegado a Escuinapa huyendo de la violencia en Durango fueron desplazadas de nuevo desde diciembre de 2025, cuando los enfrentamientos destruyeron viviendas junto al arroyo Buñigas; no figuran en el padrón estatal. Fecha aproximada. Ubicación aproximada (cabecera de Escuinapa).</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>mco-chihuahua</t>
+          <t>noroeste</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>https://www.eldiariodechihuahua.mx/estado/2026/sep/24/llegan-desplazados-de-durango-y-sinaloa-840648.html</t>
+          <t>https://www.noroeste.com.mx/mazatlan/dejaron-durango-huyendo-de-la-violencia-y-llegaron-a-escuinapa-donde-tambien-han-tenido-que-escapar-GB23220512</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -3237,53 +3237,53 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ev-030</t>
+          <t>ev-056</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
+          <t>periodistas</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>acoso judicial</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>19.088</v>
+        <v>19.043</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>-102.353</v>
+        <v>-98.19799999999999</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Apatzingán, Michoacán</t>
+          <t>Puebla, Puebla</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Balaceras desplazan a 668 personas de cinco comunidades de Apatzingán</t>
+          <t>Vinculación a proceso del director del portal e-consulta por su labor periodística</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>El Observatorio de Seguridad Humana de la Región Apatzingán registró la salida de 314 personas de Holanda, 168 de Cueramato, 123 de Guanajuatillo, 58 de El Mezquital y 5 de Los Laureles tras enfrentamientos entre grupos criminales; exigió aplicar el Reglamento municipal de respuesta a emergencias de desplazamiento. Ubicación aproximada (cabecera municipal).</t>
+          <t>ARTICLE 19 señaló el caso como precedente grave de uso del derecho penal para intimidar. En 2025 documentó 69 periodistas y medios víctimas de acoso judicial en 21 entidades. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>oshra</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>https://www.meganoticias.mx/morelia/noticia/violencia-desplaza-familias-en-apatzingan-michoacan-sigue-sin-cifras-oficiales/733651</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
@@ -3300,58 +3300,58 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>ev-031</t>
+          <t>ev-057</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
+          <t>periodistas</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>acoso judicial</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>17.595</v>
+        <v>18.134</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>-99.17700000000001</v>
+        <v>-94.422</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Alcozacán, Chilapa de Álvarez, Guerrero</t>
+          <t>Coatzacoalcos, Veracruz</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>Comunidades nahuas de Chilapa huyen a Alcozacán por ataques con drones explosivos</t>
+          <t>Fiscalía de Veracruz imputa a periodista por terrorismo por hechos ligados a su labor</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Entre el 6 y el 11 de mayo, ataques atribuidos a Los Ardillos con armas de alto calibre y drones cargados con explosivos vaciaron Tula, Xicotlán y Acahuehuetlán; entre 800 y más de mil 300 personas se refugiaron en la iglesia y la cancha de Alcozacán. La cifra oficial reconoció 96 desplazados y seis heridos. El saldo incluyó seis muertos, casas quemadas y ganado muerto. Ubicación aproximada (cabecera de Chilapa).</t>
+          <t>La imputación fue desestimada, pero se mantenían vigentes otras dos. ARTICLE 19 la calificó como uno de los episodios más alarmantes del año. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>sillarota</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>https://lasillarota.com/estados/2026/5/14/casas-quemadas-ganado-muerto-96-desplazados-el-saldo-en-chilapa-por-los-ardillos-510079.html</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -3363,7 +3363,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>ev-062</t>
+          <t>ev-058</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -3373,48 +3373,48 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>informe</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>19.432</v>
+        <v>20.533</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>-99.133</v>
+        <v>-97.459</v>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Poza Rica, Veracruz</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>ARTICLE 19: 451 agresiones a la prensa en 2025, siete asesinatos y ocho tentativas</t>
+          <t>Asesinato de Carlos Castro en Poza Rica</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Informe Estructuras del silencio. Una agresión cada 19 horas; 44 por ciento ambiente hostil, 34 abuso del poder público, 12 violencia física. El Estado fue el agresor en 227 casos. Ciudad de México, Puebla y Veracruz encabezan; Sinaloa registra solo nueve casos, lo que la organización atribuye a autocensura y a denuncias por canales confidenciales. 2025 fue también el año más letal para personas buscadoras (siete asesinatos y cuatro desapariciones). Cifra nacional ubicada en la capital.</t>
+          <t>Asesinado el 8 de enero dentro de un restaurante de la avenida 20 de Noviembre, primer periodista asesinado en 2026 según el recuento de N+ y CPJ. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>nmas</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+          <t>https://www.nmas.com.mx/seguridad/asesinatos/cuantos-y-quienes-son-los-periodistas-asesinados-en-mexico-este-2026/</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -3426,7 +3426,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>ev-032</t>
+          <t>ev-026</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3436,48 +3436,48 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>retorno</t>
+          <t>desplazamiento masivo</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>17.595</v>
+        <v>24.765</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>-99.17700000000001</v>
+        <v>-107.702</v>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez, Guerrero</t>
+          <t>Las Puentes, Navolato, Sinaloa</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>Retorno de 120 personas a Tula, Xicotlán y Coatzingo con escolta de la Guardia Nacional</t>
+          <t>Familias de Las Puentes se dispersan hacia Culiacán, Villa Juárez y El Diez</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Tras cinco días fuera de sus hogares, 120 personas comenzaron a regresar con apoyo de la Guardia Nacional y un corredor seguro de la Defensa; la titular de Segob supervisó el retorno. Ubicación aproximada (cabecera de Chilapa).</t>
+          <t>Sebides informó que en enero recorrió Las Puentes, donde algunas personas permanecieron y otras se trasladaron a Culiacán, Villa Juárez y El Diez; la dependencia seguía localizando a las familias. Ubicación aproximada (cabecera de Navolato).</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>elfinanciero</t>
+          <t>sebides</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>https://www.elfinanciero.com.mx/estados/2026/05/14/familias-indigenas-desplazadas-por-violencia-de-los-ardillos-en-chilapa-regresan-a-sus-comunidades/</t>
+          <t>https://www.aztecasinaloa.com/noticias/en-sinaloa-familias-se-desplazan-por-violencia-cuales-son-los-municipios-afectados/</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>oficial</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3489,7 +3489,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>ev-063</t>
+          <t>ev-059</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
@@ -3515,27 +3515,27 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>La Conquista, Culiacán, Sinaloa</t>
+          <t>Culiacán, Sinaloa</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Militares golpean a dos periodistas acreditados durante un operativo</t>
+          <t>Policía estatal apunta su arma contra reportero de la fuente de seguridad</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Elementos del Ejército golpearon y empujaron a dos periodistas identificados y arrebataron un teléfono; un agente del GOES estatal intervino para protegerlos. El Instituto documentó 125 agresiones entre agosto de 2022 y febrero de 2026, 45 atribuidas a particulares presuntamente vinculados con el crimen. Ubicación aproximada (cabecera municipal).</t>
+          <t>Tras un enfrentamiento entre fuerzas de seguridad y un grupo armado, agentes de la Policía Estatal Preventiva agredieron a un reportero; el hecho quedó en video. El Instituto de Protección documentó 235 agresiones al gremio entre 2022 y 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>revistaespejo</t>
+          <t>proceso</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>https://revistaespejo.com/2026/05/14/periodistas-de-culiacan-acusan-agresiones-por-parte-de-militares/</t>
+          <t>https://www.proceso.com.mx/nacional/estados/2026/1/19/policia-estatal-de-sinaloa-apunta-su-arma-hacia-reportero-en-culiacan-video-366842.html</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
@@ -3552,58 +3552,58 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>ev-064</t>
+          <t>ev-027</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>periodistas</t>
+          <t>desplazamiento</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>cifra gremial</t>
+          <t>desplazamiento masivo</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>24.809</v>
+        <v>26.095</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>-107.394</v>
+        <v>-106.965</v>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Culiacán, Sinaloa</t>
+          <t>Atascaderos, Guadalupe y Calvo, Chihuahua</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>Asociación 7 de Junio: más de 100 incidentes contra periodistas desde septiembre de 2024</t>
+          <t>Unas 600 personas desplazadas del seccional Atascaderos por enfrentamientos entre facciones</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>El presidente de la asociación denunció que menos de 20 casos se han formalizado ante la vicefiscalía especializada y que las autoridades reclasifican agresiones como robos sin analizar el contexto periodístico. Ubicación aproximada (cabecera municipal).</t>
+          <t>Entre el 18 y el 27 de febrero cientos de personas, en su mayoría indígenas, fueron atendidas en albergues de Chihuahua capital y Parral; otras llegaron a Cuauhtémoc y Delicias. Un mes después unas 200 regresaron con acompañamiento policial y militar. Organizaciones como Alianza Sierra Madre y Contec advierten un desplazamiento silencioso que ha vaciado pueblos. Ubicación aproximada (cabecera de Guadalupe y Calvo).</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>asociacion-7-junio</t>
+          <t>elimparcial</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>https://www.sectorprimario.mx/2026/05/15/mas-de-100-agresiones-silencian-al-periodismo-en-sinaloa/</t>
+          <t>https://www.elimparcial.com/mexico/2026/04/18/indigenas-raramuri-son-desplazados-por-la-violencia-del-crimen-organizado-en-la-sierra-tarahumara-mientras-organizaciones-civiles-alertan-abandono-del-estado-y-una-crisis-humanitaria-que-ya-afecta-a-miles-de-familias-en-chihuahua/</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -3615,7 +3615,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>ev-033</t>
+          <t>ev-028</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -3625,48 +3625,48 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>retorno</t>
+          <t>cifra oficial</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>19.088</v>
+        <v>24.809</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>-102.353</v>
+        <v>-107.394</v>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Apatzingán, Michoacán</t>
+          <t>Culiacán, Sinaloa</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Cerca de 20 familias regresan a Holanda, Cueramato, Guanajuatillo y otras comunidades</t>
+          <t>Sebides: padrón de unas 3 mil personas y mil 300 familias más desde noviembre de 2025</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Según el Observatorio de Seguridad Humana, unas 20 familias desplazadas por los enfrentamientos del 5 de mayo retornaron a sus comunidades en la zona rural de Apatzingán. Ubicación aproximada (cabecera municipal).</t>
+          <t>El titular de Sebides informó un padrón de alrededor de 3 mil personas en desplazamiento forzado interno y mil 300 familias adicionales detectadas desde finales de 2025; Culiacán, Mazatlán y Guasave concentran la llegada. Se anunció el programa Viviendas para el Bienestar para víctimas sin casa propia. Cifra estatal ubicada en la capital.</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>milenio</t>
+          <t>sebides</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>https://www.milenio.com/estados/regresan-familias-tras-ser-desplazadas-por-la-violencia-en-apatzingan</t>
+          <t>https://revistaespejo.com/2026/03/14/gobierno-de-sinaloa-registra-mas-de-4-mil-personas-desplazadas/</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>oficial</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -3678,58 +3678,58 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>ev-034</t>
+          <t>ev-060</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
+          <t>periodistas</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>retorno</t>
+          <t>asesinato de persona defensora</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>22.647</v>
+        <v>19.392</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>-102.994</v>
+        <v>-101.278</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Palmas Altas, Jerez, Zacatecas</t>
+          <t>El Zangarro, Villa Madero, Michoacán</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>Familias desplazadas regresan a Palmas Altas y otras comunidades de Jerez</t>
+          <t>Asesinato de Roberto Chávez, Comité de Defensa Ambiental de El Zangarro</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Con el control militar de la zona y la firma de un acuerdo para construir un cuartel regional en Palmas Altas, la mayoría de los habitantes retomó actividades agrícolas, aunque con temor y con familiares desaparecidos. Ubicación aproximada (cabecera de Jerez).</t>
+          <t>Defensor ambiental de 64 años, asesinado a balazos la noche del 12 de abril al regresar a su casa. CEMDA contabiliza al menos 195 personas defensoras ambientales asesinadas en México entre 2016 y 2026. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>unotv</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>https://www.unotv.com/estados/zacatecas/con-temor-desplazados-por-la-violencia-regresan-a-comunidades-serranas-de-zacatecas/</t>
+          <t>https://grupoanimal.mx/explicaciones/defensores-ambientales-asesinados-mexico</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -3741,7 +3741,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>ev-065</t>
+          <t>ev-061</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3751,48 +3751,48 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>secuestro y asesinato de periodista</t>
+          <t>desaparición y asesinato de persona defensora</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>17.995</v>
+        <v>19.401</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>-94.348</v>
+        <v>-101.732</v>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Moloacán, Veracruz</t>
+          <t>Zirahuén, Salvador Escalante, Michoacán</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Roxana Guzmán Ramírez, Pulso Informativo del Sureste, secuestrada y hallada sin vida</t>
+          <t>Lázaro Mendoza Ramírez, defensor de la región lacustre de Zirahuén, desaparecido y hallado sin vida</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Sacada de su casa por hombres armados el 2 de junio de 2026; sus restos fueron identificados el 3 de julio en un predio de Moloacán. Las autoridades señalaron a funcionarios municipales como responsables, según CPJ. Ubicación aproximada (cabecera municipal).</t>
+          <t>Desaparecido el 14 de abril; su cuerpo fue localizado calcinado en su camioneta e identificado por ADN. Segundo defensor ambiental asesinado en Michoacán en menos de una semana. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>excelsior</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>https://www.excelsior.com.mx/nacional/suma-mexico-seis-periodistas-asesinados-2026-cpj-exige-frenar-ataques-y-fin-impunidad</t>
+          <t>https://grupoanimal.mx/sociedad/ambientalistas-asesinados-semana-michoacan</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -3804,58 +3804,58 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>ev-066</t>
+          <t>ev-029</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>periodistas</t>
+          <t>desplazamiento</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>cifra oficial</t>
+          <t>desplazamiento masivo</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>24.809</v>
+        <v>24.968</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>-107.394</v>
+        <v>-106.965</v>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Culiacán, Sinaloa</t>
+          <t>Tamazula, Durango</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>Instituto de Protección alerta repunte de agresiones desde marzo de 2026</t>
+          <t>Al menos 368 personas desplazadas de Tamazula por enfrentamientos y amenazas de reclutamiento</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>133 medidas de protección activadas en 2026, 27 quejas entre enero y abril, y 12 periodistas que han salido del estado por amenazas en los últimos años. Agresiones tanto de fuerzas de seguridad como de grupos armados, incluidas mujeres periodistas en cobertura. Ubicación aproximada (cabecera municipal).</t>
+          <t>Según el informe sobre desplazamiento forzado en Chihuahua (mayo de 2026), al menos 368 personas de Tamazula, en el Triángulo Dorado, salieron por enfrentamientos, bloqueos de rutas, desabasto y amenazas de reclutamiento de jóvenes; la cabecera solo es accesible por aire desde El Durazno. Fecha del informe. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>instituto-sinaloa</t>
+          <t>mco-chihuahua</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>https://noticieroaltavoz.com/este-7-de-junio-dia-de-la-libertad-de-expresion-alertan-por-repunte-de-agresiones-contra-periodistas-en-sinaloa/</t>
+          <t>https://www.eldiariodechihuahua.mx/estado/2026/sep/24/llegan-desplazados-de-durango-y-sinaloa-840648.html</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -3867,7 +3867,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>ev-035</t>
+          <t>ev-030</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3882,43 +3882,43 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>22.837</v>
+        <v>19.088</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>-105.776</v>
+        <v>-102.353</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Escuinapa, Sinaloa</t>
+          <t>Apatzingán, Michoacán</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Comunidades rurales de Escuinapa quedan vacías; familias buscan refugio en Nayarit y Mazatlán</t>
+          <t>Balaceras desplazan a 668 personas de cinco comunidades de Apatzingán</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>La CEDH inició la documentación de familias desplazadas por la escalada de violencia iniciada a mediados de diciembre de 2025 (coche bomba, ataques al ayuntamiento, homicidios). El alcalde negó un desplazamiento masivo pero reconoció salidas en Tecualilla, Palmillas y El Camarón. Ubicación aproximada (cabecera municipal).</t>
+          <t>El Observatorio de Seguridad Humana de la Región Apatzingán registró la salida de 314 personas de Holanda, 168 de Cueramato, 123 de Guanajuatillo, 58 de El Mezquital y 5 de Los Laureles tras enfrentamientos entre grupos criminales; exigió aplicar el Reglamento municipal de respuesta a emergencias de desplazamiento. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>infobae</t>
+          <t>oshra</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/mexico/2026/06/11/violencia-en-escuinapa-desata-desplazamiento-de-habitantes-cedh-inicia-documentacion-de-casos/</t>
+          <t>https://www.meganoticias.mx/morelia/noticia/violencia-desplaza-familias-en-apatzingan-michoacan-sigue-sin-cifras-oficiales/733651</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -3930,58 +3930,58 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>ev-067</t>
+          <t>ev-031</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>periodistas</t>
+          <t>desplazamiento</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>desplazamiento masivo</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>20.533</v>
+        <v>17.595</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>-97.459</v>
+        <v>-99.17700000000001</v>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Poza Rica, Veracruz</t>
+          <t>Alcozacán, Chilapa de Álvarez, Guerrero</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Luis Ángel López Valdez, Reportaje Policiaco Veracruzano</t>
+          <t>Comunidades nahuas de Chilapa huyen a Alcozacán por ataques con drones explosivos</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Asesinado a balazos la madrugada del 11 de junio en la colonia Cazones, cerca de donde fue asesinado Carlos Castro en enero. Contaba con medidas de acompañamiento y vigilancia. Ubicación aproximada (cabecera municipal).</t>
+          <t>Entre el 6 y el 11 de mayo, ataques atribuidos a Los Ardillos con armas de alto calibre y drones cargados con explosivos vaciaron Tula, Xicotlán y Acahuehuetlán; entre 800 y más de mil 300 personas se refugiaron en la iglesia y la cancha de Alcozacán. La cifra oficial reconoció 96 desplazados y seis heridos. El saldo incluyó seis muertos, casas quemadas y ganado muerto. Ubicación aproximada (cabecera de Chilapa).</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>rsf</t>
+          <t>sillarota</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>https://rsf.org/es/m%C3%A9xico-el-asesinato-de-francisco-alejandro-leyva-aguilar-s%C3%A9ptimo-periodista-asesinado-en-2026</t>
+          <t>https://lasillarota.com/estados/2026/5/14/casas-quemadas-ganado-muerto-96-desplazados-el-saldo-en-chilapa-por-los-ardillos-510079.html</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -3993,58 +3993,58 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>ev-036</t>
+          <t>ev-062</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
+          <t>periodistas</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>informe</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>26.095</v>
+        <v>19.432</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>-106.965</v>
+        <v>-99.133</v>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Guadalupe y Calvo, Chihuahua</t>
+          <t>Ciudad de México</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Tres comunidades ódami (Milpillas de Abajo, La Arenosa y Arroyo Azul) desplazadas tras enfrentamiento</t>
+          <t>ARTICLE 19: 451 agresiones a la prensa en 2025, siete asesinatos y ocho tentativas</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Un enfrentamiento entre dos grupos armados por la entrada de un nuevo cártel al Triángulo Dorado desplazó a tres comunidades ódami. El Diario de Chihuahua estima que entre 2016 y 2026 al menos 11 mil 534 personas han sido expulsadas de la sierra. Ubicación aproximada (cabecera municipal).</t>
+          <t>Informe Estructuras del silencio. Una agresión cada 19 horas; 44 por ciento ambiente hostil, 34 abuso del poder público, 12 violencia física. El Estado fue el agresor en 227 casos. Ciudad de México, Puebla y Veracruz encabezan; Sinaloa registra solo nueve casos, lo que la organización atribuye a autocensura y a denuncias por canales confidenciales. 2025 fue también el año más letal para personas buscadoras (siete asesinatos y cuatro desapariciones). Cifra nacional ubicada en la capital.</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>diariochihuahua</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>https://www.eldiariodechihuahua.mx/estado/2026/jul/10/desplazo-crimen-a-mas-de-11-mil-en-la-sierra-816155.html</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -4056,7 +4056,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>ev-037</t>
+          <t>ev-032</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -4066,48 +4066,48 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>cifra oficial</t>
+          <t>retorno</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>25.363</v>
+        <v>17.595</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>-107.551</v>
+        <v>-99.17700000000001</v>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Badiraguato, Sinaloa</t>
+          <t>Chilapa de Álvarez, Guerrero</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>Sebides: más de 3 mil familias desplazadas, concentradas en Badiraguato, Concordia y San Ignacio</t>
+          <t>Retorno de 120 personas a Tula, Xicotlán y Coatzingo con escolta de la Guardia Nacional</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>La dependencia informó que los casos se concentran en municipios con zonas serranas como Badiraguato, Concordia y San Ignacio, y que también hay desplazamientos por fenómenos naturales y falta de infraestructura. Ubicación aproximada (cabecera municipal).</t>
+          <t>Tras cinco días fuera de sus hogares, 120 personas comenzaron a regresar con apoyo de la Guardia Nacional y un corredor seguro de la Defensa; la titular de Segob supervisó el retorno. Ubicación aproximada (cabecera de Chilapa).</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>elfinanciero</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>https://www.aztecasinaloa.com/noticias/violencia-deja-a-mas-3-mil-familias-desplazadas-en-las-comunidades-serranas-sinaloa</t>
+          <t>https://www.elfinanciero.com.mx/estados/2026/05/14/familias-indigenas-desplazadas-por-violencia-de-los-ardillos-en-chilapa-regresan-a-sus-comunidades/</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -4119,7 +4119,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>ev-068</t>
+          <t>ev-063</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4129,48 +4129,48 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>desaparición y asesinato de periodista</t>
+          <t>agresión por autoridad</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>17.643</v>
+        <v>24.809</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>-101.552</v>
+        <v>-107.394</v>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta, Guerrero</t>
+          <t>La Conquista, Culiacán, Sinaloa</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Alex Serna, periodista ambiental, desaparecido el 20 de junio y asesinado</t>
+          <t>Militares golpean a dos periodistas acreditados durante un operativo</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Moreno Serna, periodista ambiental independiente, fue reportado desaparecido el 20 de junio tras denuncias sobre tala y daños en la región del río Salitreras; un audio atribuido a él afirmaba estar secuestrado en represalia. RSF lo registra como asesinado el 3 de julio. Ubicación aproximada (cabecera municipal).</t>
+          <t>Elementos del Ejército golpearon y empujaron a dos periodistas identificados y arrebataron un teléfono; un agente del GOES estatal intervino para protegerlos. El Instituto documentó 125 agresiones entre agosto de 2022 y febrero de 2026, 45 atribuidas a particulares presuntamente vinculados con el crimen. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>rsf</t>
+          <t>revistaespejo</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>https://rsf.org/es/alex-serna-especializado-en-temas-ambientales-es-el-quinto-periodista-asesinado-en-m%C3%A9xico-desde</t>
+          <t>https://revistaespejo.com/2026/05/14/periodistas-de-culiacan-acusan-agresiones-por-parte-de-militares/</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -4182,58 +4182,58 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>ev-038</t>
+          <t>ev-064</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
+          <t>periodistas</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>cifra gremial</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>18.74</v>
+        <v>24.809</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>-102.788</v>
+        <v>-107.394</v>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Franja serrana Apatzingán-Aguililla, Michoacán</t>
+          <t>Culiacán, Sinaloa</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>Alrededor de 400 personas dejan comunidades entre Apatzingán y Aguililla</t>
+          <t>Asociación 7 de Junio: más de 100 incidentes contra periodistas desde septiembre de 2024</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>El dirigente estatal del PRI afirmó que en el último mes y medio unas 400 personas abandonaron El Aguaje, El Naranjo Viejo, El Naranjo de Chila, Las Bateas y Loma de los Hoyos por la disputa entre grupos criminales. Cifra de un actor político, sin confirmación oficial. Ubicación aproximada (cabecera de Aguililla).</t>
+          <t>El presidente de la asociación denunció que menos de 20 casos se han formalizado ante la vicefiscalía especializada y que las autoridades reclasifican agresiones como robos sin analizar el contexto periodístico. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>quadratin</t>
+          <t>asociacion-7-junio</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>https://www.quadratin.com.mx/justicia/suman-400-desplazados-en-apatzingan-y-aguililla-durante-el-ultimo-mes/</t>
+          <t>https://www.sectorprimario.mx/2026/05/15/mas-de-100-agresiones-silencian-al-periodismo-en-sinaloa/</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -4245,7 +4245,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>ev-039</t>
+          <t>ev-033</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4255,43 +4255,43 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>retorno</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>27.865</v>
+        <v>19.088</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>-108.235</v>
+        <v>-102.353</v>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Uruachi y Moris, Chihuahua</t>
+          <t>Apatzingán, Michoacán</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Cerca de 10 comunidades indígenas de Moris y Uruachi salen por ataques con explosivos desde drones</t>
+          <t>Cerca de 20 familias regresan a Holanda, Cueramato, Guanajuatillo y otras comunidades</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Entre junio y julio de 2026 comunidades de Moris y Uruachi abandonaron sus territorios por ataques del grupo Los Salazar, con explosivos lanzados desde drones, según El Diario de Chihuahua. Fecha aproximada. Ubicación aproximada (cabecera de Uruachi).</t>
+          <t>Según el Observatorio de Seguridad Humana, unas 20 familias desplazadas por los enfrentamientos del 5 de mayo retornaron a sus comunidades en la zona rural de Apatzingán. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>diariochihuahua</t>
+          <t>milenio</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>https://www.eldiariodechihuahua.mx/estado/2026/jul/10/desplazo-crimen-a-mas-de-11-mil-en-la-sierra-816155.html</t>
+          <t>https://www.milenio.com/estados/regresan-familias-tras-ser-desplazadas-por-la-violencia-en-apatzingan</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
@@ -4308,7 +4308,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>ev-040</t>
+          <t>ev-034</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4318,43 +4318,43 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>retorno</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>26.095</v>
+        <v>22.647</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>-106.965</v>
+        <v>-102.994</v>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Cinco Llagas, Guadalupe y Calvo, Chihuahua</t>
+          <t>Palmas Altas, Jerez, Zacatecas</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>Llegan a Chihuahua 17 personas desplazadas de Cinco Llagas</t>
+          <t>Familias desplazadas regresan a Palmas Altas y otras comunidades de Jerez</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>La titular de la Comisión estatal de desplazamiento forzado informó el traslado de familias de Cinco Llagas para recibir atención, mientras comunidades de la sierra permanecen sin abasto de productos básicos por la inseguridad. Ubicación aproximada (cabecera municipal).</t>
+          <t>Con el control militar de la zona y la firma de un acuerdo para construir un cuartel regional en Palmas Altas, la mayoría de los habitantes retomó actividades agrícolas, aunque con temor y con familiares desaparecidos. Ubicación aproximada (cabecera de Jerez).</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>heraldochihuahua</t>
+          <t>unotv</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>https://oem.com.mx/elheraldodechihuahua/local/llegan-a-chihuahua-17-desplazados-por-violencia-comunidades-de-guadalupe-y-calvo-enfrentan-crisis-por-falta-de-alimentos-31001267</t>
+          <t>https://www.unotv.com/estados/zacatecas/con-temor-desplazados-por-la-violencia-regresan-a-comunidades-serranas-de-zacatecas/</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -4371,7 +4371,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>ev-069</t>
+          <t>ev-065</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4381,48 +4381,48 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>secuestro y asesinato de periodista</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>19.284</v>
+        <v>17.995</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>-98.43899999999999</v>
+        <v>-94.348</v>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>San Martín Texmelucan, Puebla</t>
+          <t>Moloacán, Veracruz</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Josué Martínez Contreras, director de Noticias San Martín Texmelucan</t>
+          <t>Roxana Guzmán Ramírez, Pulso Informativo del Sureste, secuestrada y hallada sin vida</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Asesinado a tiros el 16 de julio. Una ex autoridad local señalada por amenazas previas fue detenida dos días después por otro delito. ARTICLE 19 documentó 39 agresiones en Puebla en 2025, la segunda cifra del país. Ubicación aproximada (cabecera municipal).</t>
+          <t>Sacada de su casa por hombres armados el 2 de junio de 2026; sus restos fueron identificados el 3 de julio en un predio de Moloacán. Las autoridades señalaron a funcionarios municipales como responsables, según CPJ. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>rsf</t>
+          <t>excelsior</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>https://rsf.org/es/m%C3%A9xico-sexto-periodista-asesinado-en-2026-el-gobierno-debe-actuar-con-urgencia-frente-la-violencia</t>
+          <t>https://www.excelsior.com.mx/nacional/suma-mexico-seis-periodistas-asesinados-2026-cpj-exige-frenar-ataques-y-fin-impunidad</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -4434,7 +4434,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>ev-070</t>
+          <t>ev-066</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>ataque a medio</t>
+          <t>cifra oficial</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
@@ -4465,27 +4465,27 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>Ataque armado contra domicilio vinculado al director de Grupo Adiscusión</t>
+          <t>Instituto de Protección alerta repunte de agresiones desde marzo de 2026</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>El Instituto de Protección condenó el ataque y pidió investigar la posible relación con la actividad periodística de la víctima. Ubicación aproximada (cabecera municipal).</t>
+          <t>133 medidas de protección activadas en 2026, 27 quejas entre enero y abril, y 12 periodistas que han salido del estado por amenazas en los últimos años. Agresiones tanto de fuerzas de seguridad como de grupos armados, incluidas mujeres periodistas en cobertura. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>noroeste</t>
+          <t>instituto-sinaloa</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>https://www.noroeste.com.mx/culiacan/instituto-de-proteccion-a-periodistas-condena-ataque-contra-domicilio-vinculado-a-director-de-adiscusion-HP24187055</t>
+          <t>https://noticieroaltavoz.com/este-7-de-junio-dia-de-la-libertad-de-expresion-alertan-por-repunte-de-agresiones-contra-periodistas-en-sinaloa/</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>oficial</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -4497,58 +4497,58 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>ev-071</t>
+          <t>ev-035</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>periodistas</t>
+          <t>desplazamiento</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>desplazamiento masivo</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>17.146</v>
+        <v>22.837</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>-96.752</v>
+        <v>-105.776</v>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>San Pablo Etla, Oaxaca</t>
+          <t>Escuinapa, Sinaloa</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Francisco Alejandro Leyva Aguilar, periodista y articulista</t>
+          <t>Comunidades rurales de Escuinapa quedan vacías; familias buscan refugio en Nayarit y Mazatlán</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Asesinado a tiros el 22 de julio; un año antes había denunciado oficialmente amenazas de muerte. Séptimo periodista asesinado en 2026 según RSF, sexto según CPJ. Ubicación aproximada (cabecera municipal).</t>
+          <t>La CEDH inició la documentación de familias desplazadas por la escalada de violencia iniciada a mediados de diciembre de 2025 (coche bomba, ataques al ayuntamiento, homicidios). El alcalde negó un desplazamiento masivo pero reconoció salidas en Tecualilla, Palmillas y El Camarón. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>rsf</t>
+          <t>infobae</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>https://rsf.org/es/m%C3%A9xico-el-asesinato-de-francisco-alejandro-leyva-aguilar-s%C3%A9ptimo-periodista-asesinado-en-2026</t>
+          <t>https://www.infobae.com/mexico/2026/06/11/violencia-en-escuinapa-desata-desplazamiento-de-habitantes-cedh-inicia-documentacion-de-casos/</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
@@ -4560,58 +4560,58 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>ev-041</t>
+          <t>ev-067</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
+          <t>periodistas</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>cruce de frontera</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>15.664</v>
+        <v>20.533</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>-92.14</v>
+        <v>-97.459</v>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Frontera Comalapa, Chiapas</t>
+          <t>Poza Rica, Veracruz</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>60 personas huyen de Frontera Comalapa a Huehuetenango, Guatemala</t>
+          <t>Asesinato de Luis Ángel López Valdez, Reportaje Policiaco Veracruzano</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>El Procurador de Derechos Humanos de Guatemala informó del ingreso de al menos 60 personas mexicanas desplazadas a la aldea Guaila, La Democracia, Huehuetenango, tras el asesinato del comisariado ejidal de El Sabinalito dos días antes. Guatemala envió ayuda humanitaria. Ubicación aproximada (cabecera municipal).</t>
+          <t>Asesinado a balazos la madrugada del 11 de junio en la colonia Cazones, cerca de donde fue asesinado Carlos Castro en enero. Contaba con medidas de acompañamiento y vigilancia. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>aztecachiapas</t>
+          <t>rsf</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>https://www.aztecachiapas.com/noticias/familias-de-chiapas-buscan-refugio-en-guatemala-por-la-violencia/</t>
+          <t>https://rsf.org/es/m%C3%A9xico-el-asesinato-de-francisco-alejandro-leyva-aguilar-s%C3%A9ptimo-periodista-asesinado-en-2026</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -4623,7 +4623,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>ev-042</t>
+          <t>ev-036</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>informe</t>
+          <t>desplazamiento masivo</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -4654,27 +4654,27 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>Misión Civil de Observación: 4 mil 492 personas desplazadas de la sierra Tarahumara en 2025</t>
+          <t>Tres comunidades ódami (Milpillas de Abajo, La Arenosa y Arroyo Azul) desplazadas tras enfrentamiento</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>El informe de la Misión Civil de Observación (Red TDT, Tlachinollan, Serapaz) documentó en mayo de 2026 a unas 200 personas desplazadas en Parral, Delicias y Chihuahua, provenientes de Atascaderos, Coloradas de la Virgen, La Sierrita, Uruachi y Guazapares, además de Tamazula (Durango) y San Miguel (Sinaloa). Entre 2023 y septiembre de 2025 hubo 83 denuncias por desplazamiento ante la fiscalía estatal y dos sentencias. Cifra regional ubicada en el municipio más afectado.</t>
+          <t>Un enfrentamiento entre dos grupos armados por la entrada de un nuevo cártel al Triángulo Dorado desplazó a tres comunidades ódami. El Diario de Chihuahua estima que entre 2016 y 2026 al menos 11 mil 534 personas han sido expulsadas de la sierra. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>mco-chihuahua</t>
+          <t>diariochihuahua</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>https://www.jornada.com.mx/2026/08/12/estados/026n1est</t>
+          <t>https://www.eldiariodechihuahua.mx/estado/2026/jul/10/desplazo-crimen-a-mas-de-11-mil-en-la-sierra-816155.html</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -4686,58 +4686,58 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>ev-072</t>
+          <t>ev-037</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>periodistas</t>
+          <t>desplazamiento</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>informe</t>
+          <t>cifra oficial</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>19.432</v>
+        <v>25.363</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>-99.133</v>
+        <v>-107.551</v>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Badiraguato, Sinaloa</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>Espacio OSC: el Mecanismo rechazó 70 por ciento de las solicitudes de protección entre 2024 y junio de 2026</t>
+          <t>Sebides: más de 3 mil familias desplazadas, concentradas en Badiraguato, Concordia y San Ignacio</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>De 409 solicitudes recibidas, 289 fueron rechazadas; las organizaciones señalan que algunas personas han perdido la vida con medidas o esperando incorporación. Al 31 de mayo de 2026 el Mecanismo protegía a 2 mil 20 personas (690 periodistas y mil 330 defensoras). Cifra nacional ubicada en la capital.</t>
+          <t>La dependencia informó que los casos se concentran en municipios con zonas serranas como Badiraguato, Concordia y San Ignacio, y que también hay desplazamientos por fenómenos naturales y falta de infraestructura. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>espacio-osc</t>
+          <t>sebides</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>https://www.proceso.com.mx/nacional/2026/9/4/osc-urge-al-gobierno-federal-a-fortalecer-mecanismo-de-proteccion-para-defensores-y-periodistas-379345.html</t>
+          <t>https://www.aztecasinaloa.com/noticias/violencia-deja-a-mas-3-mil-familias-desplazadas-en-las-comunidades-serranas-sinaloa</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>oficial</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
@@ -4749,215 +4749,695 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
+          <t>ev-068</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>desaparición y asesinato de periodista</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>17.643</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>-101.552</v>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Zihuatanejo de Azueta, Guerrero</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Alex Serna, periodista ambiental, desaparecido el 20 de junio y asesinado</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Moreno Serna, periodista ambiental independiente, fue reportado desaparecido el 20 de junio tras denuncias sobre tala y daños en la región del río Salitreras; un audio atribuido a él afirmaba estar secuestrado en represalia. RSF lo registra como asesinado el 3 de julio. Ubicación aproximada (cabecera municipal).</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>rsf</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>https://rsf.org/es/alex-serna-especializado-en-temas-ambientales-es-el-quinto-periodista-asesinado-en-m%C3%A9xico-desde</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>organización</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>ev-038</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>desplazamiento</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>desplazamiento masivo</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>-102.788</v>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Franja serrana Apatzingán-Aguililla, Michoacán</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Alrededor de 400 personas dejan comunidades entre Apatzingán y Aguililla</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>El dirigente estatal del PRI afirmó que en el último mes y medio unas 400 personas abandonaron El Aguaje, El Naranjo Viejo, El Naranjo de Chila, Las Bateas y Loma de los Hoyos por la disputa entre grupos criminales. Cifra de un actor político, sin confirmación oficial. Ubicación aproximada (cabecera de Aguililla).</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>quadratin</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>https://www.quadratin.com.mx/justicia/suman-400-desplazados-en-apatzingan-y-aguililla-durante-el-ultimo-mes/</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>prensa</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>ev-039</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>desplazamiento</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>desplazamiento masivo</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>27.865</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>-108.235</v>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Uruachi y Moris, Chihuahua</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Cerca de 10 comunidades indígenas de Moris y Uruachi salen por ataques con explosivos desde drones</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Entre junio y julio de 2026 comunidades de Moris y Uruachi abandonaron sus territorios por ataques del grupo Los Salazar, con explosivos lanzados desde drones, según El Diario de Chihuahua. Fecha aproximada. Ubicación aproximada (cabecera de Uruachi).</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>diariochihuahua</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>https://www.eldiariodechihuahua.mx/estado/2026/jul/10/desplazo-crimen-a-mas-de-11-mil-en-la-sierra-816155.html</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>prensa</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>ev-040</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>desplazamiento</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>desplazamiento masivo</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>26.095</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>-106.965</v>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Cinco Llagas, Guadalupe y Calvo, Chihuahua</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Llegan a Chihuahua 17 personas desplazadas de Cinco Llagas</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>La titular de la Comisión estatal de desplazamiento forzado informó el traslado de familias de Cinco Llagas para recibir atención, mientras comunidades de la sierra permanecen sin abasto de productos básicos por la inseguridad. Ubicación aproximada (cabecera municipal).</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>heraldochihuahua</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>https://oem.com.mx/elheraldodechihuahua/local/llegan-a-chihuahua-17-desplazados-por-violencia-comunidades-de-guadalupe-y-calvo-enfrentan-crisis-por-falta-de-alimentos-31001267</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>prensa</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>ev-069</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>asesinato de periodista</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>19.284</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>-98.43899999999999</v>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>San Martín Texmelucan, Puebla</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Asesinato de Josué Martínez Contreras, director de Noticias San Martín Texmelucan</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Asesinado a tiros el 16 de julio. Una ex autoridad local señalada por amenazas previas fue detenida dos días después por otro delito. ARTICLE 19 documentó 39 agresiones en Puebla en 2025, la segunda cifra del país. Ubicación aproximada (cabecera municipal).</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>rsf</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>https://rsf.org/es/m%C3%A9xico-sexto-periodista-asesinado-en-2026-el-gobierno-debe-actuar-con-urgencia-frente-la-violencia</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>organización</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>ev-070</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>ataque a medio</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>24.809</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>-107.394</v>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Culiacán, Sinaloa</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Ataque armado contra domicilio vinculado al director de Grupo Adiscusión</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>El Instituto de Protección condenó el ataque y pidió investigar la posible relación con la actividad periodística de la víctima. Ubicación aproximada (cabecera municipal).</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>noroeste</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>https://www.noroeste.com.mx/culiacan/instituto-de-proteccion-a-periodistas-condena-ataque-contra-domicilio-vinculado-a-director-de-adiscusion-HP24187055</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>prensa</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>ev-071</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>asesinato de periodista</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>17.146</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>-96.752</v>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>San Pablo Etla, Oaxaca</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Asesinato de Francisco Alejandro Leyva Aguilar, periodista y articulista</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Asesinado a tiros el 22 de julio; un año antes había denunciado oficialmente amenazas de muerte. Séptimo periodista asesinado en 2026 según RSF, sexto según CPJ. Ubicación aproximada (cabecera municipal).</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>rsf</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>https://rsf.org/es/m%C3%A9xico-el-asesinato-de-francisco-alejandro-leyva-aguilar-s%C3%A9ptimo-periodista-asesinado-en-2026</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>organización</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>ev-041</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>desplazamiento</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>cruce de frontera</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>15.664</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>-92.14</v>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Frontera Comalapa, Chiapas</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>60 personas huyen de Frontera Comalapa a Huehuetenango, Guatemala</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>El Procurador de Derechos Humanos de Guatemala informó del ingreso de al menos 60 personas mexicanas desplazadas a la aldea Guaila, La Democracia, Huehuetenango, tras el asesinato del comisariado ejidal de El Sabinalito dos días antes. Guatemala envió ayuda humanitaria. Ubicación aproximada (cabecera municipal).</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>aztecachiapas</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aztecachiapas.com/noticias/familias-de-chiapas-buscan-refugio-en-guatemala-por-la-violencia/</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>prensa</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>ev-042</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>desplazamiento</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>informe</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>26.095</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>-106.965</v>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Guadalupe y Calvo, Chihuahua</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Misión Civil de Observación: 4 mil 492 personas desplazadas de la sierra Tarahumara en 2025</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>El informe de la Misión Civil de Observación (Red TDT, Tlachinollan, Serapaz) documentó en mayo de 2026 a unas 200 personas desplazadas en Parral, Delicias y Chihuahua, provenientes de Atascaderos, Coloradas de la Virgen, La Sierrita, Uruachi y Guazapares, además de Tamazula (Durango) y San Miguel (Sinaloa). Entre 2023 y septiembre de 2025 hubo 83 denuncias por desplazamiento ante la fiscalía estatal y dos sentencias. Cifra regional ubicada en el municipio más afectado.</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>mco-chihuahua</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jornada.com.mx/2026/08/12/estados/026n1est</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>organización</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>ev-072</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>informe</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>19.432</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>-99.133</v>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Ciudad de México</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Espacio OSC: el Mecanismo rechazó 70 por ciento de las solicitudes de protección entre 2024 y junio de 2026</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>De 409 solicitudes recibidas, 289 fueron rechazadas; las organizaciones señalan que algunas personas han perdido la vida con medidas o esperando incorporación. Al 31 de mayo de 2026 el Mecanismo protegía a 2 mil 20 personas (690 periodistas y mil 330 defensoras). Cifra nacional ubicada en la capital.</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>espacio-osc</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>https://www.proceso.com.mx/nacional/2026/9/4/osc-urge-al-gobierno-federal-a-fortalecer-mecanismo-de-proteccion-para-defensores-y-periodistas-379345.html</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>organización</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
           <t>ev-043</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>desplazamiento</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>informe</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E69" s="3" t="n">
+      <c r="E79" s="3" t="n">
         <v>16.753</v>
       </c>
-      <c r="F69" s="3" t="n">
+      <c r="F79" s="3" t="n">
         <v>-93.116</v>
       </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="G79" s="5" t="inlineStr">
         <is>
           <t>Tuxtla Gutiérrez, Chiapas</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>Frayba documenta 24 mil 290 personas desplazadas en Chiapas entre 2021 y octubre de 2025</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>El informe Chiapas, la paz pendiente (mayo de 2026) contabiliza 24 mil 290 personas desplazadas en Pantelhó, Frontera Comalapa, Chicomuselo, Oxchuc, Las Margaritas, Huixtán, Chenalhó, Ocosingo, La Trinitaria, Socoltenango, La Concordia, Bella Vista y Tila. El gobierno estatal sostiene que 95 por ciento ha regresado; el Frayba advierte que los retornos no siempre son duraderos. Cifra estatal ubicada en la capital.</t>
         </is>
       </c>
-      <c r="J69" s="3" t="inlineStr">
+      <c r="J79" s="3" t="inlineStr">
         <is>
           <t>frayba</t>
         </is>
       </c>
-      <c r="K69" s="3" t="inlineStr">
+      <c r="K79" s="3" t="inlineStr">
         <is>
           <t>https://www.jornada.com.mx/noticia/2026/05/26/opinion/desplazados-chiapas-la-vida-y-el-miedo</t>
         </is>
       </c>
-      <c r="L69" s="3" t="inlineStr">
+      <c r="L79" s="3" t="inlineStr">
         <is>
           <t>organización</t>
         </is>
       </c>
-      <c r="M69" s="3" t="inlineStr">
+      <c r="M79" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="n"/>
-      <c r="B70" s="6" t="n"/>
-      <c r="C70" s="6" t="n"/>
-      <c r="D70" s="7" t="n"/>
-      <c r="E70" s="6" t="n"/>
-      <c r="F70" s="6" t="n"/>
-      <c r="G70" s="6" t="n"/>
-      <c r="H70" s="6" t="n"/>
-      <c r="I70" s="6" t="n"/>
-      <c r="J70" s="6" t="n"/>
-      <c r="K70" s="6" t="n"/>
-      <c r="L70" s="6" t="n"/>
-      <c r="M70" s="6" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="n"/>
-      <c r="B71" s="6" t="n"/>
-      <c r="C71" s="6" t="n"/>
-      <c r="D71" s="7" t="n"/>
-      <c r="E71" s="6" t="n"/>
-      <c r="F71" s="6" t="n"/>
-      <c r="G71" s="6" t="n"/>
-      <c r="H71" s="6" t="n"/>
-      <c r="I71" s="6" t="n"/>
-      <c r="J71" s="6" t="n"/>
-      <c r="K71" s="6" t="n"/>
-      <c r="L71" s="6" t="n"/>
-      <c r="M71" s="6" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="n"/>
-      <c r="B72" s="6" t="n"/>
-      <c r="C72" s="6" t="n"/>
-      <c r="D72" s="7" t="n"/>
-      <c r="E72" s="6" t="n"/>
-      <c r="F72" s="6" t="n"/>
-      <c r="G72" s="6" t="n"/>
-      <c r="H72" s="6" t="n"/>
-      <c r="I72" s="6" t="n"/>
-      <c r="J72" s="6" t="n"/>
-      <c r="K72" s="6" t="n"/>
-      <c r="L72" s="6" t="n"/>
-      <c r="M72" s="6" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="n"/>
-      <c r="B73" s="6" t="n"/>
-      <c r="C73" s="6" t="n"/>
-      <c r="D73" s="7" t="n"/>
-      <c r="E73" s="6" t="n"/>
-      <c r="F73" s="6" t="n"/>
-      <c r="G73" s="6" t="n"/>
-      <c r="H73" s="6" t="n"/>
-      <c r="I73" s="6" t="n"/>
-      <c r="J73" s="6" t="n"/>
-      <c r="K73" s="6" t="n"/>
-      <c r="L73" s="6" t="n"/>
-      <c r="M73" s="6" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="n"/>
-      <c r="B74" s="6" t="n"/>
-      <c r="C74" s="6" t="n"/>
-      <c r="D74" s="7" t="n"/>
-      <c r="E74" s="6" t="n"/>
-      <c r="F74" s="6" t="n"/>
-      <c r="G74" s="6" t="n"/>
-      <c r="H74" s="6" t="n"/>
-      <c r="I74" s="6" t="n"/>
-      <c r="J74" s="6" t="n"/>
-      <c r="K74" s="6" t="n"/>
-      <c r="L74" s="6" t="n"/>
-      <c r="M74" s="6" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="n"/>
-      <c r="B75" s="6" t="n"/>
-      <c r="C75" s="6" t="n"/>
-      <c r="D75" s="7" t="n"/>
-      <c r="E75" s="6" t="n"/>
-      <c r="F75" s="6" t="n"/>
-      <c r="G75" s="6" t="n"/>
-      <c r="H75" s="6" t="n"/>
-      <c r="I75" s="6" t="n"/>
-      <c r="J75" s="6" t="n"/>
-      <c r="K75" s="6" t="n"/>
-      <c r="L75" s="6" t="n"/>
-      <c r="M75" s="6" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="n"/>
-      <c r="B76" s="6" t="n"/>
-      <c r="C76" s="6" t="n"/>
-      <c r="D76" s="7" t="n"/>
-      <c r="E76" s="6" t="n"/>
-      <c r="F76" s="6" t="n"/>
-      <c r="G76" s="6" t="n"/>
-      <c r="H76" s="6" t="n"/>
-      <c r="I76" s="6" t="n"/>
-      <c r="J76" s="6" t="n"/>
-      <c r="K76" s="6" t="n"/>
-      <c r="L76" s="6" t="n"/>
-      <c r="M76" s="6" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="n"/>
-      <c r="B77" s="6" t="n"/>
-      <c r="C77" s="6" t="n"/>
-      <c r="D77" s="7" t="n"/>
-      <c r="E77" s="6" t="n"/>
-      <c r="F77" s="6" t="n"/>
-      <c r="G77" s="6" t="n"/>
-      <c r="H77" s="6" t="n"/>
-      <c r="I77" s="6" t="n"/>
-      <c r="J77" s="6" t="n"/>
-      <c r="K77" s="6" t="n"/>
-      <c r="L77" s="6" t="n"/>
-      <c r="M77" s="6" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="n"/>
-      <c r="B78" s="6" t="n"/>
-      <c r="C78" s="6" t="n"/>
-      <c r="D78" s="7" t="n"/>
-      <c r="E78" s="6" t="n"/>
-      <c r="F78" s="6" t="n"/>
-      <c r="G78" s="6" t="n"/>
-      <c r="H78" s="6" t="n"/>
-      <c r="I78" s="6" t="n"/>
-      <c r="J78" s="6" t="n"/>
-      <c r="K78" s="6" t="n"/>
-      <c r="L78" s="6" t="n"/>
-      <c r="M78" s="6" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="n"/>
-      <c r="B79" s="6" t="n"/>
-      <c r="C79" s="6" t="n"/>
-      <c r="D79" s="7" t="n"/>
-      <c r="E79" s="6" t="n"/>
-      <c r="F79" s="6" t="n"/>
-      <c r="G79" s="6" t="n"/>
-      <c r="H79" s="6" t="n"/>
-      <c r="I79" s="6" t="n"/>
-      <c r="J79" s="6" t="n"/>
-      <c r="K79" s="6" t="n"/>
-      <c r="L79" s="6" t="n"/>
-      <c r="M79" s="6" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
